--- a/assets/AccountstoCheck-LSEG_NewCols.xlsx
+++ b/assets/AccountstoCheck-LSEG_NewCols.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevinat\Documents\GitHub\lseg-registrations\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A213ACA-D23B-475B-BC3A-65D7CD4EDCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DDB0CC-D09E-4BF5-93BD-971910058A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17726" yWindow="1269" windowWidth="24685" windowHeight="13097" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19389" yWindow="2931" windowWidth="24685" windowHeight="13098" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$B$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$B$1:$L$1</definedName>
     <definedName name="IQ_CH">110000</definedName>
     <definedName name="IQ_CQ">5000</definedName>
     <definedName name="IQ_CY">10000</definedName>
@@ -162,11 +162,35 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Integer count of licenses in LSEG admin portal; Add during lookup step</t>
+Yes or No; Add during lookup step</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{D6132E2E-95C0-43D3-9509-0800F71E4890}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{9E18F4E9-E5F5-4B29-841E-52D57FC82845}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Kevin Thomas:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Yes or No; Add during lookup step</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{D6132E2E-95C0-43D3-9509-0800F71E4890}">
       <text>
         <r>
           <rPr>
@@ -190,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{FACEEC03-0CCF-4DCD-9BE4-2F6FA4B5E577}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{FACEEC03-0CCF-4DCD-9BE4-2F6FA4B5E577}">
       <text>
         <r>
           <rPr>
@@ -214,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{09F74AAD-B738-4ED2-88B1-A6C679BAB2A3}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{09F74AAD-B738-4ED2-88B1-A6C679BAB2A3}">
       <text>
         <r>
           <rPr>
@@ -234,11 +258,11 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Columns L-O fill automatically</t>
+Columns M-P fill automatically</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{2CBDEE67-D79F-4FD1-BC56-CB3F4FEB5A51}">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{2CBDEE67-D79F-4FD1-BC56-CB3F4FEB5A51}">
       <text>
         <r>
           <rPr>
@@ -262,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{F2E0EFE6-AF5A-4DC5-B3DC-801F190B3823}">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{F2E0EFE6-AF5A-4DC5-B3DC-801F190B3823}">
       <text>
         <r>
           <rPr>
@@ -282,7 +306,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Columns Q-S fill automatically</t>
+Columns R-T fill automatically</t>
         </r>
       </text>
     </comment>
@@ -291,7 +315,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Number</t>
   </si>
@@ -348,6 +372,9 @@
   </si>
   <si>
     <t>Email_local-part</t>
+  </si>
+  <si>
+    <t>Has duplicate in backend</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.26953125" customWidth="1"/>
@@ -1237,13 +1264,13 @@
     <col min="6" max="6" width="16.7265625" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.54296875" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.54296875" customWidth="1"/>
-    <col min="9" max="9" width="22.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.54296875" customWidth="1"/>
-    <col min="11" max="11" width="52.1796875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.54296875" customWidth="1"/>
+    <col min="9" max="10" width="22.453125" customWidth="1"/>
+    <col min="11" max="11" width="15.54296875" customWidth="1"/>
+    <col min="12" max="12" width="52.1796875" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1272,33 +1299,36 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
